--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.3/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.3/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H3">
         <v>426</v>
